--- a/docs/member_a/成员一_WBF模块1测试用例与结果.xlsx
+++ b/docs/member_a/成员一_WBF模块1测试用例与结果.xlsx
@@ -1570,7 +1570,7 @@
       <c r="I9" s="9" t="n"/>
       <c r="J9" s="11" t="inlineStr">
         <is>
-          <t>2026-09-11T09:32:21.354014+08:00</t>
+          <t>2026-09-11T09:33:18.234915+08:00</t>
         </is>
       </c>
       <c r="K9" s="11" t="n"/>
@@ -2733,7 +2733,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="42" customHeight="1">
+    <row r="6" ht="120" customHeight="1">
       <c r="A6" s="124" t="inlineStr">
         <is>
           <t>WBF-UT-005</t>
@@ -2774,11 +2774,33 @@
           <t>boxes=[[[0.1,0.1,0.5,0.5]],[[0.12,0.12,0.52,0.52]]]; scores=[[0.9],[0.8]]; labels=[[1],[1]]; weights=[1,1]; iou_thr=0.55</t>
         </is>
       </c>
-      <c r="I6" s="120" t="n"/>
-      <c r="J6" s="120" t="n"/>
-      <c r="K6" s="120" t="n"/>
-      <c r="L6" s="120" t="n"/>
-      <c r="M6" s="120" t="n"/>
+      <c r="I6" s="140" t="inlineStr">
+        <is>
+          <t>1. 载入test_data/member_a/WBF-UT-005.json输入。2. 使用成功复现虚拟环境运行对应pytest用例。3. 捕获返回值、形状、警告及异常，与执行前的独立预期核对。4. 保存批次日志/JSON并回填结果。</t>
+        </is>
+      </c>
+      <c r="J6" s="140" t="inlineStr">
+        <is>
+          <t>返回1框，坐标约[0.1094117647,0.1094117647,0.5094117647,0.5094117647]，分数0.85，类别1。</t>
+        </is>
+      </c>
+      <c r="K6" s="140" t="inlineStr">
+        <is>
+          <t>{"scenario":"spreadsheet_input","output":{"boxes":[[0.10941176116466522,0.10941176116466522,0.5094117522239685,0.5094117522239685]],"scores":[0.8500000238418579],"labels":[1.0]},"shapes":[[1,4],[1],[1]],"exception":null,"warnings":[],"stdout":""}</t>
+        </is>
+      </c>
+      <c r="L6" s="141" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M6" s="140" t="inlineStr">
+        <is>
+          <t>等价类与手工加权计算；交集0.38²=0.1444，并集0.1756，IoU=361/439≈0.822323&gt;0.55；坐标以0.9和0.8加权，分数=(0.9+0.8)/2。
+执行时间：2026-09-11T09:33:18.234915+08:00；Python 3.10.16 / NumPy 1.23.5 / pytest 9.0.3
+运行前源码提交：fe56ca815668aa0bf985e9ba317905484128cd4f；WBF 与 reproduction-success 一致：True；证据：manual_tests/member_a/results/batch_02/results.json</t>
+        </is>
+      </c>
       <c r="N6" s="43" t="n"/>
     </row>
     <row r="7" ht="42" customHeight="1">
@@ -2829,7 +2851,7 @@
       <c r="M7" s="120" t="n"/>
       <c r="N7" s="43" t="n"/>
     </row>
-    <row r="8" ht="42" customHeight="1">
+    <row r="8" ht="120" customHeight="1">
       <c r="A8" s="124" t="inlineStr">
         <is>
           <t>WBF-UT-007</t>
@@ -2870,11 +2892,36 @@
           <t>boxes=[[[0.1,0.1,0.5,0.5]],[[0.2161290323,0.1,0.6161290323,0.5]]]; scores=[[0.9],[0.8]]; labels=[[1],[1]]; weights=[1,1]; iou_thr=0.55</t>
         </is>
       </c>
-      <c r="I8" s="120" t="n"/>
-      <c r="J8" s="120" t="n"/>
-      <c r="K8" s="120" t="n"/>
-      <c r="L8" s="120" t="n"/>
-      <c r="M8" s="120" t="n"/>
+      <c r="I8" s="140" t="inlineStr">
+        <is>
+          <t>1. 载入test_data/member_a/WBF-UT-007.json输入。2. 使用成功复现虚拟环境运行对应pytest用例。3. 捕获返回值、形状、警告及异常，与执行前的独立预期核对。4. 保存批次日志/JSON并回填结果。</t>
+        </is>
+      </c>
+      <c r="J8" s="140" t="inlineStr">
+        <is>
+          <t>原输入返回2框，分数[0.45,0.4]。补充IoU精确为0.5的数据：阈值0.5不融合；紧邻其下的浮点阈值融合；紧邻其上的阈值不融合。</t>
+        </is>
+      </c>
+      <c r="K8" s="140" t="inlineStr">
+        <is>
+          <t>{"scenario":"spreadsheet_input","output":{"boxes":[[0.1,0.1,0.5,0.5],[0.2161290323,0.1,0.6161290323,0.5]],"scores":[0.45,0.4],"labels":[1.0,1.0]},"shapes":[[2,4],[2],[2]],"exception":null,"warnings":[],"stdout":""}
+{"scenario":"exact_iou_equals_threshold","output":{"boxes":[[0.0,0.0,0.75,1.0],[0.25,0.0,1.0,1.0]],"scores":[0.45,0.4],"labels":[1.0,1.0]},"shapes":[[2,4],[2],[2]],"exception":null,"warnings":[],"stdout":""}
+{"scenario":"threshold_one_float_below_iou","output":{"boxes":[[0.11764705926179886,0.0,0.8676470518112183,0.9999999403953552]],"scores":[0.8500000238418579],"labels":[1.0]},"shapes":[[1,4],[1],[1]],"exception":null,"warnings":[],"stdout":""}
+{"scenario":"threshold_one_float_above_iou","output":{"boxes":[[0.0,0.0,0.75,1.0],[0.25,0.0,1.0,1.0]],"scores":[0.45,0.4],"labels":[1.0,1.0]},"shapes":[[2,4],[2],[2]],"exception":null,"warnings":[],"stdout":""}</t>
+        </is>
+      </c>
+      <c r="L8" s="141" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M8" s="140" t="inlineStr">
+        <is>
+          <t>边界值：原输入及精确等值/相邻浮点阈值；原表坐标经截断后IoU≈0.549999999864375，并非恰等于0.55。保留原输入，额外用二进制可精确表示的坐标验证等值边界，不能只凭原输入宣称覆盖等值。
+执行时间：2026-09-11T09:33:18.234915+08:00；Python 3.10.16 / NumPy 1.23.5 / pytest 9.0.3
+运行前源码提交：fe56ca815668aa0bf985e9ba317905484128cd4f；WBF 与 reproduction-success 一致：True；证据：manual_tests/member_a/results/batch_02/results.json</t>
+        </is>
+      </c>
       <c r="N8" s="43" t="n"/>
     </row>
     <row r="9" ht="42" customHeight="1">
@@ -41783,12 +41830,24 @@
       </c>
       <c r="C4" s="143" t="inlineStr">
         <is>
-          <t>待执行</t>
-        </is>
-      </c>
-      <c r="D4" s="143" t="n"/>
-      <c r="E4" s="143" t="n"/>
-      <c r="F4" s="143" t="n"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D4" s="143" t="inlineStr">
+        <is>
+          <t>2026-09-11T09:33:18.234915+08:00</t>
+        </is>
+      </c>
+      <c r="E4" s="143" t="inlineStr">
+        <is>
+          <t>fe56ca815668aa0bf985e9ba317905484128cd4f</t>
+        </is>
+      </c>
+      <c r="F4" s="143" t="inlineStr">
+        <is>
+          <t>manual_tests/member_a/results/batch_02/results.json</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="143" t="inlineStr">
@@ -41803,12 +41862,24 @@
       </c>
       <c r="C5" s="143" t="inlineStr">
         <is>
-          <t>待执行</t>
-        </is>
-      </c>
-      <c r="D5" s="143" t="n"/>
-      <c r="E5" s="143" t="n"/>
-      <c r="F5" s="143" t="n"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D5" s="143" t="inlineStr">
+        <is>
+          <t>2026-09-11T09:33:18.234915+08:00</t>
+        </is>
+      </c>
+      <c r="E5" s="143" t="inlineStr">
+        <is>
+          <t>fe56ca815668aa0bf985e9ba317905484128cd4f</t>
+        </is>
+      </c>
+      <c r="F5" s="143" t="inlineStr">
+        <is>
+          <t>manual_tests/member_a/results/batch_02/results.json</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="143" t="inlineStr">

--- a/docs/member_a/成员一_WBF模块1测试用例与结果.xlsx
+++ b/docs/member_a/成员一_WBF模块1测试用例与结果.xlsx
@@ -1570,7 +1570,7 @@
       <c r="I9" s="9" t="n"/>
       <c r="J9" s="11" t="inlineStr">
         <is>
-          <t>2026-09-11T09:33:18.234915+08:00</t>
+          <t>2026-09-11T09:33:52.434390+08:00</t>
         </is>
       </c>
       <c r="K9" s="11" t="n"/>
@@ -2972,7 +2972,7 @@
       <c r="M9" s="120" t="n"/>
       <c r="N9" s="43" t="n"/>
     </row>
-    <row r="10" ht="42" customHeight="1">
+    <row r="10" ht="120" customHeight="1">
       <c r="A10" s="124" t="inlineStr">
         <is>
           <t>WBF-UT-009</t>
@@ -3013,11 +3013,33 @@
           <t>boxes=[[[0.1,0.1,0.5,0.5]],[[0.1,0.1,0.5,0.5]]]; scores=[[0.9],[0.8]]; labels=[[1],[1]]; weights=[1,1]; iou_thr=1</t>
         </is>
       </c>
-      <c r="I10" s="120" t="n"/>
-      <c r="J10" s="120" t="n"/>
-      <c r="K10" s="120" t="n"/>
-      <c r="L10" s="120" t="n"/>
-      <c r="M10" s="120" t="n"/>
+      <c r="I10" s="140" t="inlineStr">
+        <is>
+          <t>1. 载入test_data/member_a/WBF-UT-009.json输入。2. 使用成功复现虚拟环境运行对应pytest用例。3. 捕获返回值、形状、警告及异常，与执行前的独立预期核对。4. 保存批次日志/JSON并回填结果。</t>
+        </is>
+      </c>
+      <c r="J10" s="140" t="inlineStr">
+        <is>
+          <t>相同框IoU=1，与阈值相等，不融合；返回2个相同坐标框，分数[0.45,0.4]、类别[1,1]。</t>
+        </is>
+      </c>
+      <c r="K10" s="140" t="inlineStr">
+        <is>
+          <t>{"scenario":"spreadsheet_input","output":{"boxes":[[0.1,0.1,0.5,0.5],[0.1,0.1,0.5,0.5]],"scores":[0.45,0.4],"labels":[1.0,1.0]},"shapes":[[2,4],[2],[2]],"exception":null,"warnings":[],"stdout":""}</t>
+        </is>
+      </c>
+      <c r="L10" s="141" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M10" s="140" t="inlineStr">
+        <is>
+          <t>边界值：IoU阈值上界1；匹配条件是严格大于，不是大于等于。
+执行时间：2026-09-11T09:33:52.434390+08:00；Python 3.10.16 / NumPy 1.23.5 / pytest 9.0.3
+运行前源码提交：d679c884af1a7017b48216c18f22f72a5d8d26bf；WBF 与 reproduction-success 一致：True；证据：manual_tests/member_a/results/batch_03/results.json</t>
+        </is>
+      </c>
       <c r="N10" s="43" t="n"/>
     </row>
     <row r="11" ht="42" customHeight="1">
@@ -3068,7 +3090,7 @@
       <c r="M11" s="120" t="n"/>
       <c r="N11" s="43" t="n"/>
     </row>
-    <row r="12" ht="42" customHeight="1">
+    <row r="12" ht="120" customHeight="1">
       <c r="A12" s="124" t="inlineStr">
         <is>
           <t>WBF-UT-011</t>
@@ -3109,11 +3131,33 @@
           <t>boxes=[[[0.1,0.1,0.5,0.5]]]; scores=[[0.2]]; labels=[[1]]; weights=[1]; skip_box_thr=0.5</t>
         </is>
       </c>
-      <c r="I12" s="120" t="n"/>
-      <c r="J12" s="120" t="n"/>
-      <c r="K12" s="120" t="n"/>
-      <c r="L12" s="120" t="n"/>
-      <c r="M12" s="120" t="n"/>
+      <c r="I12" s="140" t="inlineStr">
+        <is>
+          <t>1. 载入test_data/member_a/WBF-UT-011.json输入。2. 使用成功复现虚拟环境运行对应pytest用例。3. 捕获返回值、形状、警告及异常，与执行前的独立预期核对。4. 保存批次日志/JSON并回填结果。</t>
+        </is>
+      </c>
+      <c r="J12" s="140" t="inlineStr">
+        <is>
+          <t>0.2&lt;0.5，全部过滤；返回形状(0,4)、(0,)、(0,)的空数组，无警告。</t>
+        </is>
+      </c>
+      <c r="K12" s="140" t="inlineStr">
+        <is>
+          <t>{"scenario":"spreadsheet_input","output":{"boxes":[],"scores":[],"labels":[]},"shapes":[[0,4],[0],[0]],"exception":null,"warnings":[],"stdout":""}</t>
+        </is>
+      </c>
+      <c r="L12" s="141" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M12" s="140" t="inlineStr">
+        <is>
+          <t>等价类：低于分数过滤阈值；原始分数在聚类前过滤。
+执行时间：2026-09-11T09:33:52.434390+08:00；Python 3.10.16 / NumPy 1.23.5 / pytest 9.0.3
+运行前源码提交：d679c884af1a7017b48216c18f22f72a5d8d26bf；WBF 与 reproduction-success 一致：True；证据：manual_tests/member_a/results/batch_03/results.json</t>
+        </is>
+      </c>
       <c r="N12" s="43" t="n"/>
     </row>
     <row r="13" ht="42" customHeight="1">
@@ -41894,12 +41938,24 @@
       </c>
       <c r="C6" s="143" t="inlineStr">
         <is>
-          <t>待执行</t>
-        </is>
-      </c>
-      <c r="D6" s="143" t="n"/>
-      <c r="E6" s="143" t="n"/>
-      <c r="F6" s="143" t="n"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D6" s="143" t="inlineStr">
+        <is>
+          <t>2026-09-11T09:33:52.434390+08:00</t>
+        </is>
+      </c>
+      <c r="E6" s="143" t="inlineStr">
+        <is>
+          <t>d679c884af1a7017b48216c18f22f72a5d8d26bf</t>
+        </is>
+      </c>
+      <c r="F6" s="143" t="inlineStr">
+        <is>
+          <t>manual_tests/member_a/results/batch_03/results.json</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="143" t="inlineStr">
@@ -41914,12 +41970,24 @@
       </c>
       <c r="C7" s="143" t="inlineStr">
         <is>
-          <t>待执行</t>
-        </is>
-      </c>
-      <c r="D7" s="143" t="n"/>
-      <c r="E7" s="143" t="n"/>
-      <c r="F7" s="143" t="n"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D7" s="143" t="inlineStr">
+        <is>
+          <t>2026-09-11T09:33:52.434390+08:00</t>
+        </is>
+      </c>
+      <c r="E7" s="143" t="inlineStr">
+        <is>
+          <t>d679c884af1a7017b48216c18f22f72a5d8d26bf</t>
+        </is>
+      </c>
+      <c r="F7" s="143" t="inlineStr">
+        <is>
+          <t>manual_tests/member_a/results/batch_03/results.json</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="143" t="inlineStr">

--- a/docs/member_a/成员一_WBF模块1测试用例与结果.xlsx
+++ b/docs/member_a/成员一_WBF模块1测试用例与结果.xlsx
@@ -1570,7 +1570,7 @@
       <c r="I9" s="9" t="n"/>
       <c r="J9" s="11" t="inlineStr">
         <is>
-          <t>2026-09-11T09:33:52.434390+08:00</t>
+          <t>2026-09-11T09:34:27.731564+08:00</t>
         </is>
       </c>
       <c r="K9" s="11" t="n"/>
@@ -3208,7 +3208,7 @@
       <c r="M13" s="120" t="n"/>
       <c r="N13" s="43" t="n"/>
     </row>
-    <row r="14" ht="42" customHeight="1">
+    <row r="14" ht="120" customHeight="1">
       <c r="A14" s="124" t="inlineStr">
         <is>
           <t>WBF-UT-013</t>
@@ -3249,11 +3249,33 @@
           <t>boxes=[[[0,0,1,1]]]; scores=[[0.9]]; labels=[[1]]; weights=[1]</t>
         </is>
       </c>
-      <c r="I14" s="120" t="n"/>
-      <c r="J14" s="120" t="n"/>
-      <c r="K14" s="120" t="n"/>
-      <c r="L14" s="120" t="n"/>
-      <c r="M14" s="120" t="n"/>
+      <c r="I14" s="140" t="inlineStr">
+        <is>
+          <t>1. 载入test_data/member_a/WBF-UT-013.json输入。2. 使用成功复现虚拟环境运行对应pytest用例。3. 捕获返回值、形状、警告及异常，与执行前的独立预期核对。4. 保存批次日志/JSON并回填结果。</t>
+        </is>
+      </c>
+      <c r="J14" s="140" t="inlineStr">
+        <is>
+          <t>返回1框[0,0,1,1]，分数0.9，类别1；不裁剪、不警告。</t>
+        </is>
+      </c>
+      <c r="K14" s="140" t="inlineStr">
+        <is>
+          <t>{"scenario":"spreadsheet_input","output":{"boxes":[[0.0,0.0,1.0,1.0]],"scores":[0.9],"labels":[1.0]},"shapes":[[1,4],[1],[1]],"exception":null,"warnings":[],"stdout":""}</t>
+        </is>
+      </c>
+      <c r="L14" s="141" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M14" s="140" t="inlineStr">
+        <is>
+          <t>边界值：合法坐标0与1；闭区间端点0和1合法，面积为1。
+执行时间：2026-09-11T09:34:27.731564+08:00；Python 3.10.16 / NumPy 1.23.5 / pytest 9.0.3
+运行前源码提交：92ac4de7b79a33a81353ed8fbdadc394a45d106b；WBF 与 reproduction-success 一致：True；证据：manual_tests/member_a/results/batch_04/results.json</t>
+        </is>
+      </c>
       <c r="N14" s="43" t="n"/>
     </row>
     <row r="15" ht="42" customHeight="1">
@@ -3304,7 +3326,7 @@
       <c r="M15" s="120" t="n"/>
       <c r="N15" s="43" t="n"/>
     </row>
-    <row r="16" ht="42" customHeight="1">
+    <row r="16" ht="120" customHeight="1">
       <c r="A16" s="124" t="inlineStr">
         <is>
           <t>WBF-UT-015</t>
@@ -3345,11 +3367,33 @@
           <t>boxes=[[[0.1,0.6,0.5,0.2]]]; scores=[[0.9]]; labels=[[1]]; weights=[1]</t>
         </is>
       </c>
-      <c r="I16" s="120" t="n"/>
-      <c r="J16" s="120" t="n"/>
-      <c r="K16" s="120" t="n"/>
-      <c r="L16" s="120" t="n"/>
-      <c r="M16" s="120" t="n"/>
+      <c r="I16" s="140" t="inlineStr">
+        <is>
+          <t>1. 载入test_data/member_a/WBF-UT-015.json输入。2. 使用成功复现虚拟环境运行对应pytest用例。3. 捕获返回值、形状、警告及异常，与执行前的独立预期核对。4. 保存批次日志/JSON并回填结果。</t>
+        </is>
+      </c>
+      <c r="J16" s="140" t="inlineStr">
+        <is>
+          <t>交换y端点后返回[0.1,0.2,0.5,0.6]，分数0.9，类别1；发出UserWarning，含Y2 &lt; Y1。</t>
+        </is>
+      </c>
+      <c r="K16" s="140" t="inlineStr">
+        <is>
+          <t>{"scenario":"spreadsheet_input","output":{"boxes":[[0.1,0.2,0.5,0.6]],"scores":[0.9],"labels":[1.0]},"shapes":[[1,4],[1],[1]],"exception":null,"warnings":[{"category":"UserWarning","message":"Y2 &lt; Y1 value in box. Swap them."}],"stdout":""}</t>
+        </is>
+      </c>
+      <c r="L16" s="141" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M16" s="140" t="inlineStr">
+        <is>
+          <t>异常等价类：纵向端点反向；沿用原接口的修正约定，不将有警告误判为测试失败。
+执行时间：2026-09-11T09:34:27.731564+08:00；Python 3.10.16 / NumPy 1.23.5 / pytest 9.0.3
+运行前源码提交：92ac4de7b79a33a81353ed8fbdadc394a45d106b；WBF 与 reproduction-success 一致：True；证据：manual_tests/member_a/results/batch_04/results.json</t>
+        </is>
+      </c>
       <c r="N16" s="43" t="n"/>
     </row>
     <row r="17" ht="42" customHeight="1">
@@ -42002,12 +42046,24 @@
       </c>
       <c r="C8" s="143" t="inlineStr">
         <is>
-          <t>待执行</t>
-        </is>
-      </c>
-      <c r="D8" s="143" t="n"/>
-      <c r="E8" s="143" t="n"/>
-      <c r="F8" s="143" t="n"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D8" s="143" t="inlineStr">
+        <is>
+          <t>2026-09-11T09:34:27.731564+08:00</t>
+        </is>
+      </c>
+      <c r="E8" s="143" t="inlineStr">
+        <is>
+          <t>92ac4de7b79a33a81353ed8fbdadc394a45d106b</t>
+        </is>
+      </c>
+      <c r="F8" s="143" t="inlineStr">
+        <is>
+          <t>manual_tests/member_a/results/batch_04/results.json</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="143" t="inlineStr">
@@ -42022,12 +42078,24 @@
       </c>
       <c r="C9" s="143" t="inlineStr">
         <is>
-          <t>待执行</t>
-        </is>
-      </c>
-      <c r="D9" s="143" t="n"/>
-      <c r="E9" s="143" t="n"/>
-      <c r="F9" s="143" t="n"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D9" s="143" t="inlineStr">
+        <is>
+          <t>2026-09-11T09:34:27.731564+08:00</t>
+        </is>
+      </c>
+      <c r="E9" s="143" t="inlineStr">
+        <is>
+          <t>92ac4de7b79a33a81353ed8fbdadc394a45d106b</t>
+        </is>
+      </c>
+      <c r="F9" s="143" t="inlineStr">
+        <is>
+          <t>manual_tests/member_a/results/batch_04/results.json</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="143" t="inlineStr">

--- a/docs/member_a/成员一_WBF模块1测试用例与结果.xlsx
+++ b/docs/member_a/成员一_WBF模块1测试用例与结果.xlsx
@@ -1570,7 +1570,7 @@
       <c r="I9" s="9" t="n"/>
       <c r="J9" s="11" t="inlineStr">
         <is>
-          <t>2026-09-11T09:34:27.731564+08:00</t>
+          <t>2026-09-11T09:35:01.042976+08:00</t>
         </is>
       </c>
       <c r="K9" s="11" t="n"/>
@@ -3444,7 +3444,7 @@
       <c r="M17" s="120" t="n"/>
       <c r="N17" s="43" t="n"/>
     </row>
-    <row r="18" ht="42" customHeight="1">
+    <row r="18" ht="120" customHeight="1">
       <c r="A18" s="124" t="inlineStr">
         <is>
           <t>WBF-UT-017</t>
@@ -3485,11 +3485,33 @@
           <t>boxes=[[[0.1,0.1,1.2,0.5]]]; scores=[[0.9]]; labels=[[1]]; weights=[1]</t>
         </is>
       </c>
-      <c r="I18" s="120" t="n"/>
-      <c r="J18" s="120" t="n"/>
-      <c r="K18" s="120" t="n"/>
-      <c r="L18" s="120" t="n"/>
-      <c r="M18" s="120" t="n"/>
+      <c r="I18" s="140" t="inlineStr">
+        <is>
+          <t>1. 载入test_data/member_a/WBF-UT-017.json输入。2. 使用成功复现虚拟环境运行对应pytest用例。3. 捕获返回值、形状、警告及异常，与执行前的独立预期核对。4. 保存批次日志/JSON并回填结果。</t>
+        </is>
+      </c>
+      <c r="J18" s="140" t="inlineStr">
+        <is>
+          <t>x2=1.2裁剪为1，返回[0.1,0.1,1,0.5]，分数0.9，类别1；UserWarning含X2 &gt; 1。</t>
+        </is>
+      </c>
+      <c r="K18" s="140" t="inlineStr">
+        <is>
+          <t>{"scenario":"spreadsheet_input","output":{"boxes":[[0.1,0.1,1.0,0.5]],"scores":[0.9],"labels":[1.0]},"shapes":[[1,4],[1],[1]],"exception":null,"warnings":[{"category":"UserWarning","message":"X2 &gt; 1 in box. Set it to 1. Check that you normalize boxes in [0, 1] range."}],"stdout":""}</t>
+        </is>
+      </c>
+      <c r="L18" s="141" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M18" s="140" t="inlineStr">
+        <is>
+          <t>异常等价类：坐标越上界；此用例预期裁剪，非按图像尺寸归一化。
+执行时间：2026-09-11T09:35:01.042976+08:00；Python 3.10.16 / NumPy 1.23.5 / pytest 9.0.3
+运行前源码提交：e7ca508190daedc5cf033a1d4c8f1c1f0a72cb64；WBF 与 reproduction-success 一致：True；证据：manual_tests/member_a/results/batch_05/results.json</t>
+        </is>
+      </c>
       <c r="N18" s="43" t="n"/>
     </row>
     <row r="19" ht="42" customHeight="1">
@@ -3540,7 +3562,7 @@
       <c r="M19" s="120" t="n"/>
       <c r="N19" s="43" t="n"/>
     </row>
-    <row r="20" ht="42" customHeight="1">
+    <row r="20" ht="120" customHeight="1">
       <c r="A20" s="124" t="inlineStr">
         <is>
           <t>WBF-UT-019</t>
@@ -3581,11 +3603,33 @@
           <t>boxes=[]; scores=[]; labels=[]; weights=None; iou_thr=0.55; skip_box_thr=0; conf_type='avg'</t>
         </is>
       </c>
-      <c r="I20" s="120" t="n"/>
-      <c r="J20" s="120" t="n"/>
-      <c r="K20" s="120" t="n"/>
-      <c r="L20" s="120" t="n"/>
-      <c r="M20" s="120" t="n"/>
+      <c r="I20" s="140" t="inlineStr">
+        <is>
+          <t>1. 载入test_data/member_a/WBF-UT-019.json输入。2. 使用成功复现虚拟环境运行对应pytest用例。3. 捕获返回值、形状、警告及异常，与执行前的独立预期核对。4. 保存批次日志/JSON并回填结果。</t>
+        </is>
+      </c>
+      <c r="J20" s="140" t="inlineStr">
+        <is>
+          <t>正常返回形状(0,4)、(0,)、(0,)的空数组，无警告，无异常。</t>
+        </is>
+      </c>
+      <c r="K20" s="140" t="inlineStr">
+        <is>
+          <t>{"scenario":"spreadsheet_input","output":{"boxes":[],"scores":[],"labels":[]},"shapes":[[0,4],[0],[0]],"exception":null,"warnings":[],"stdout":""}</t>
+        </is>
+      </c>
+      <c r="L20" s="141" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M20" s="140" t="inlineStr">
+        <is>
+          <t>边界值：0个模型的空输入；空输入是正常边界，不要求至少一个模型。
+执行时间：2026-09-11T09:35:01.042976+08:00；Python 3.10.16 / NumPy 1.23.5 / pytest 9.0.3
+运行前源码提交：e7ca508190daedc5cf033a1d4c8f1c1f0a72cb64；WBF 与 reproduction-success 一致：True；证据：manual_tests/member_a/results/batch_05/results.json</t>
+        </is>
+      </c>
       <c r="N20" s="43" t="n"/>
     </row>
     <row r="21" ht="42" customHeight="1">
@@ -42110,12 +42154,24 @@
       </c>
       <c r="C10" s="143" t="inlineStr">
         <is>
-          <t>待执行</t>
-        </is>
-      </c>
-      <c r="D10" s="143" t="n"/>
-      <c r="E10" s="143" t="n"/>
-      <c r="F10" s="143" t="n"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D10" s="143" t="inlineStr">
+        <is>
+          <t>2026-09-11T09:35:01.042976+08:00</t>
+        </is>
+      </c>
+      <c r="E10" s="143" t="inlineStr">
+        <is>
+          <t>e7ca508190daedc5cf033a1d4c8f1c1f0a72cb64</t>
+        </is>
+      </c>
+      <c r="F10" s="143" t="inlineStr">
+        <is>
+          <t>manual_tests/member_a/results/batch_05/results.json</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="143" t="inlineStr">
@@ -42130,12 +42186,24 @@
       </c>
       <c r="C11" s="143" t="inlineStr">
         <is>
-          <t>待执行</t>
-        </is>
-      </c>
-      <c r="D11" s="143" t="n"/>
-      <c r="E11" s="143" t="n"/>
-      <c r="F11" s="143" t="n"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D11" s="143" t="inlineStr">
+        <is>
+          <t>2026-09-11T09:35:01.042976+08:00</t>
+        </is>
+      </c>
+      <c r="E11" s="143" t="inlineStr">
+        <is>
+          <t>e7ca508190daedc5cf033a1d4c8f1c1f0a72cb64</t>
+        </is>
+      </c>
+      <c r="F11" s="143" t="inlineStr">
+        <is>
+          <t>manual_tests/member_a/results/batch_05/results.json</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="143" t="inlineStr">

--- a/docs/member_a/成员一_WBF模块1测试用例与结果.xlsx
+++ b/docs/member_a/成员一_WBF模块1测试用例与结果.xlsx
@@ -103,7 +103,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -143,6 +143,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00C6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
   </fills>
@@ -481,7 +486,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17"/>
   </cellStyleXfs>
-  <cellXfs count="144">
+  <cellXfs count="145">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -832,6 +837,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="8" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1570,7 +1578,7 @@
       <c r="I9" s="9" t="n"/>
       <c r="J9" s="11" t="inlineStr">
         <is>
-          <t>2026-09-11T09:35:01.042976+08:00</t>
+          <t>2026-09-11T09:35:40.300244+08:00</t>
         </is>
       </c>
       <c r="K9" s="11" t="n"/>
@@ -3680,7 +3688,7 @@
       <c r="M21" s="120" t="n"/>
       <c r="N21" s="43" t="n"/>
     </row>
-    <row r="22" ht="42" customHeight="1">
+    <row r="22" ht="120" customHeight="1">
       <c r="A22" s="124" t="inlineStr">
         <is>
           <t>WBF-UT-021</t>
@@ -3721,11 +3729,34 @@
           <t>boxes=[[[0.1,0.1,0.5,0.5]],[[0.1,0.1,0.5,0.5]]]; scores=[[0.9],[0.8]]; labels=[[1],[1]]; weights=None; conf_type='avg'</t>
         </is>
       </c>
-      <c r="I22" s="120" t="n"/>
-      <c r="J22" s="120" t="n"/>
-      <c r="K22" s="120" t="n"/>
-      <c r="L22" s="120" t="n"/>
-      <c r="M22" s="120" t="n"/>
+      <c r="I22" s="140" t="inlineStr">
+        <is>
+          <t>1. 载入test_data/member_a/WBF-UT-021.json输入。2. 使用成功复现虚拟环境运行对应pytest用例。3. 捕获返回值、形状、警告及异常，与执行前的独立预期核对。4. 保存批次日志/JSON并回填结果。</t>
+        </is>
+      </c>
+      <c r="J22" s="140" t="inlineStr">
+        <is>
+          <t>weights=None与weights=[1,1]都返回1个相同坐标框，分数0.85、类别1；两次输出一致。</t>
+        </is>
+      </c>
+      <c r="K22" s="140" t="inlineStr">
+        <is>
+          <t>{"scenario":"spreadsheet_input","output":{"boxes":[[0.10000000149011612,0.10000000149011612,0.4999999701976776,0.4999999701976776]],"scores":[0.8500000238418579],"labels":[1.0]},"shapes":[[1,4],[1],[1]],"exception":null,"warnings":[],"stdout":""}
+{"scenario":"explicit_unit_weights","output":{"boxes":[[0.10000000149011612,0.10000000149011612,0.4999999701976776,0.4999999701976776]],"scores":[0.8500000238418579],"labels":[1.0]},"shapes":[[1,4],[1],[1]],"exception":null,"warnings":[],"stdout":""}</t>
+        </is>
+      </c>
+      <c r="L22" s="141" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M22" s="140" t="inlineStr">
+        <is>
+          <t>默认值与变形关系：None等价于全1权重；同时与独立手算值核对，避免仅比较两次同错结果。
+执行时间：2026-09-11T09:35:40.300244+08:00；Python 3.10.16 / NumPy 1.23.5 / pytest 9.0.3
+运行前源码提交：c2f65e6fa4b2976f4621d020a885cca49234ba2e；WBF 与 reproduction-success 一致：True；证据：manual_tests/member_a/results/batch_06/results.json</t>
+        </is>
+      </c>
       <c r="N22" s="43" t="n"/>
     </row>
     <row r="23" ht="42" customHeight="1">
@@ -3776,7 +3807,7 @@
       <c r="M23" s="120" t="n"/>
       <c r="N23" s="43" t="n"/>
     </row>
-    <row r="24" ht="42" customHeight="1">
+    <row r="24" ht="120" customHeight="1">
       <c r="A24" s="124" t="inlineStr">
         <is>
           <t>WBF-UT-023</t>
@@ -3817,11 +3848,33 @@
           <t>boxes=[[[0.1,0.1,0.3,0.3],[0.4,0.4,0.6,0.6]]]; scores=[[0.9]]; labels=[[1,1]]; weights=[1]</t>
         </is>
       </c>
-      <c r="I24" s="120" t="n"/>
-      <c r="J24" s="120" t="n"/>
-      <c r="K24" s="120" t="n"/>
-      <c r="L24" s="120" t="n"/>
-      <c r="M24" s="120" t="n"/>
+      <c r="I24" s="140" t="inlineStr">
+        <is>
+          <t>1. 载入test_data/member_a/WBF-UT-023.json输入。2. 使用成功复现虚拟环境运行对应pytest用例。3. 捕获返回值、形状、警告及异常，与执行前的独立预期核对。4. 保存批次日志/JSON并回填结果。</t>
+        </is>
+      </c>
+      <c r="J24" s="140" t="inlineStr">
+        <is>
+          <t>建议契约：显式抛出ValueError且说明数量不一致，调用者可正常捕获；不能用SystemExit退出进程。</t>
+        </is>
+      </c>
+      <c r="K24" s="140" t="inlineStr">
+        <is>
+          <t>{"scenario":"spreadsheet_input","output":null,"shapes":null,"exception":{"type":"SystemExit","message":"None","exit_code":null,"traceback":"Traceback (most recent call last):\n  File \"E:\\WBF\\WBF-Software-Testing-main\\manual_tests\\member_a\\conftest.py\", line 51, in invoke\n    result = weighted_boxes_fusion(**params)\n  File \"E:\\WBF\\WBF-Software-Testing-main\\ensemble_boxes\\ensemble_boxes_wbf.py\", line 195, in weighted_boxes_fusion\n    filtered_boxes = prefilter_boxes(boxes_list, scores_list, labels_list, weights, skip_box_thr)\n  File \"E:\\WBF\\WBF-Software-Testing-main\\ensemble_boxes\\ensemble_boxes_wbf.py\", line 17, in prefilter_boxes\n    exit()\n  File \"D:\\anaconda\\lib\\_sitebuiltins.py\", line 26, in __call__\n    raise SystemExit(code)\nSystemExit: None\n"},"warnings":[],"stdout":"Error. Length of boxes arrays not equal to length of scores array: 2 != 1\n"}</t>
+        </is>
+      </c>
+      <c r="L24" s="142" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="M24" s="140" t="inlineStr">
+        <is>
+          <t>健壮性：内部框/分数数量不一致；ValueError属于本次建议的健壮性要求，原源码未承诺该异常类型；真实行为单独记录，缺陷定性待评审。
+执行时间：2026-09-11T09:35:40.300244+08:00；Python 3.10.16 / NumPy 1.23.5 / pytest 9.0.3
+运行前源码提交：c2f65e6fa4b2976f4621d020a885cca49234ba2e；WBF 与 reproduction-success 一致：True；证据：manual_tests/member_a/results/batch_06/results.json</t>
+        </is>
+      </c>
       <c r="N24" s="43" t="n"/>
     </row>
     <row r="25" ht="42" customHeight="1">
@@ -41854,456 +41907,480 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="142" t="inlineStr">
+      <c r="A1" s="143" t="inlineStr">
         <is>
           <t>编号</t>
         </is>
       </c>
-      <c r="B1" s="142" t="inlineStr">
+      <c r="B1" s="143" t="inlineStr">
         <is>
           <t>标题</t>
         </is>
       </c>
-      <c r="C1" s="142" t="inlineStr">
+      <c r="C1" s="143" t="inlineStr">
         <is>
           <t>状态</t>
         </is>
       </c>
-      <c r="D1" s="142" t="inlineStr">
+      <c r="D1" s="143" t="inlineStr">
         <is>
           <t>执行时间</t>
         </is>
       </c>
-      <c r="E1" s="142" t="inlineStr">
+      <c r="E1" s="143" t="inlineStr">
         <is>
           <t>源码提交（运行前）</t>
         </is>
       </c>
-      <c r="F1" s="142" t="inlineStr">
+      <c r="F1" s="143" t="inlineStr">
         <is>
           <t>证据路径</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="143" t="inlineStr">
+      <c r="A2" s="144" t="inlineStr">
         <is>
           <t>WBF-UT-001</t>
         </is>
       </c>
-      <c r="B2" s="143" t="inlineStr">
+      <c r="B2" s="144" t="inlineStr">
         <is>
           <t>单模型、单个合法框</t>
         </is>
       </c>
-      <c r="C2" s="143" t="inlineStr">
+      <c r="C2" s="144" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="D2" s="143" t="inlineStr">
+      <c r="D2" s="144" t="inlineStr">
         <is>
           <t>2026-09-11T09:32:21.354014+08:00</t>
         </is>
       </c>
-      <c r="E2" s="143" t="inlineStr">
+      <c r="E2" s="144" t="inlineStr">
         <is>
           <t>69fcd6ac4460450bf701c2bb1fb99623ebd7f0cc</t>
         </is>
       </c>
-      <c r="F2" s="143" t="inlineStr">
+      <c r="F2" s="144" t="inlineStr">
         <is>
           <t>manual_tests/member_a/results/batch_01/results.json</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="143" t="inlineStr">
+      <c r="A3" s="144" t="inlineStr">
         <is>
           <t>WBF-UT-003</t>
         </is>
       </c>
-      <c r="B3" s="143" t="inlineStr">
+      <c r="B3" s="144" t="inlineStr">
         <is>
           <t>双模型、完全不重叠的同类别框</t>
         </is>
       </c>
-      <c r="C3" s="143" t="inlineStr">
+      <c r="C3" s="144" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="D3" s="143" t="inlineStr">
+      <c r="D3" s="144" t="inlineStr">
         <is>
           <t>2026-09-11T09:32:21.354014+08:00</t>
         </is>
       </c>
-      <c r="E3" s="143" t="inlineStr">
+      <c r="E3" s="144" t="inlineStr">
         <is>
           <t>69fcd6ac4460450bf701c2bb1fb99623ebd7f0cc</t>
         </is>
       </c>
-      <c r="F3" s="143" t="inlineStr">
+      <c r="F3" s="144" t="inlineStr">
         <is>
           <t>manual_tests/member_a/results/batch_01/results.json</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="143" t="inlineStr">
+      <c r="A4" s="144" t="inlineStr">
         <is>
           <t>WBF-UT-005</t>
         </is>
       </c>
-      <c r="B4" s="143" t="inlineStr">
+      <c r="B4" s="144" t="inlineStr">
         <is>
           <t>同类别，IoU明显大于阈值</t>
         </is>
       </c>
-      <c r="C4" s="143" t="inlineStr">
+      <c r="C4" s="144" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="D4" s="143" t="inlineStr">
+      <c r="D4" s="144" t="inlineStr">
         <is>
           <t>2026-09-11T09:33:18.234915+08:00</t>
         </is>
       </c>
-      <c r="E4" s="143" t="inlineStr">
+      <c r="E4" s="144" t="inlineStr">
         <is>
           <t>fe56ca815668aa0bf985e9ba317905484128cd4f</t>
         </is>
       </c>
-      <c r="F4" s="143" t="inlineStr">
+      <c r="F4" s="144" t="inlineStr">
         <is>
           <t>manual_tests/member_a/results/batch_02/results.json</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="143" t="inlineStr">
+      <c r="A5" s="144" t="inlineStr">
         <is>
           <t>WBF-UT-007</t>
         </is>
       </c>
-      <c r="B5" s="143" t="inlineStr">
+      <c r="B5" s="144" t="inlineStr">
         <is>
           <t>IoU恰好等于阈值</t>
         </is>
       </c>
-      <c r="C5" s="143" t="inlineStr">
+      <c r="C5" s="144" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="D5" s="143" t="inlineStr">
+      <c r="D5" s="144" t="inlineStr">
         <is>
           <t>2026-09-11T09:33:18.234915+08:00</t>
         </is>
       </c>
-      <c r="E5" s="143" t="inlineStr">
+      <c r="E5" s="144" t="inlineStr">
         <is>
           <t>fe56ca815668aa0bf985e9ba317905484128cd4f</t>
         </is>
       </c>
-      <c r="F5" s="143" t="inlineStr">
+      <c r="F5" s="144" t="inlineStr">
         <is>
           <t>manual_tests/member_a/results/batch_02/results.json</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="143" t="inlineStr">
+      <c r="A6" s="144" t="inlineStr">
         <is>
           <t>WBF-UT-009</t>
         </is>
       </c>
-      <c r="B6" s="143" t="inlineStr">
+      <c r="B6" s="144" t="inlineStr">
         <is>
           <t>iou_thr = 1</t>
         </is>
       </c>
-      <c r="C6" s="143" t="inlineStr">
+      <c r="C6" s="144" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="D6" s="143" t="inlineStr">
+      <c r="D6" s="144" t="inlineStr">
         <is>
           <t>2026-09-11T09:33:52.434390+08:00</t>
         </is>
       </c>
-      <c r="E6" s="143" t="inlineStr">
+      <c r="E6" s="144" t="inlineStr">
         <is>
           <t>d679c884af1a7017b48216c18f22f72a5d8d26bf</t>
         </is>
       </c>
-      <c r="F6" s="143" t="inlineStr">
+      <c r="F6" s="144" t="inlineStr">
         <is>
           <t>manual_tests/member_a/results/batch_03/results.json</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="143" t="inlineStr">
+      <c r="A7" s="144" t="inlineStr">
         <is>
           <t>WBF-UT-011</t>
         </is>
       </c>
-      <c r="B7" s="143" t="inlineStr">
+      <c r="B7" s="144" t="inlineStr">
         <is>
           <t>score明显低于skip_box_thr</t>
         </is>
       </c>
-      <c r="C7" s="143" t="inlineStr">
+      <c r="C7" s="144" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="D7" s="143" t="inlineStr">
+      <c r="D7" s="144" t="inlineStr">
         <is>
           <t>2026-09-11T09:33:52.434390+08:00</t>
         </is>
       </c>
-      <c r="E7" s="143" t="inlineStr">
+      <c r="E7" s="144" t="inlineStr">
         <is>
           <t>d679c884af1a7017b48216c18f22f72a5d8d26bf</t>
         </is>
       </c>
-      <c r="F7" s="143" t="inlineStr">
+      <c r="F7" s="144" t="inlineStr">
         <is>
           <t>manual_tests/member_a/results/batch_03/results.json</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="143" t="inlineStr">
+      <c r="A8" s="144" t="inlineStr">
         <is>
           <t>WBF-UT-013</t>
         </is>
       </c>
-      <c r="B8" s="143" t="inlineStr">
+      <c r="B8" s="144" t="inlineStr">
         <is>
           <t>框坐标恰好覆盖0和1</t>
         </is>
       </c>
-      <c r="C8" s="143" t="inlineStr">
+      <c r="C8" s="144" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="D8" s="143" t="inlineStr">
+      <c r="D8" s="144" t="inlineStr">
         <is>
           <t>2026-09-11T09:34:27.731564+08:00</t>
         </is>
       </c>
-      <c r="E8" s="143" t="inlineStr">
+      <c r="E8" s="144" t="inlineStr">
         <is>
           <t>92ac4de7b79a33a81353ed8fbdadc394a45d106b</t>
         </is>
       </c>
-      <c r="F8" s="143" t="inlineStr">
+      <c r="F8" s="144" t="inlineStr">
         <is>
           <t>manual_tests/member_a/results/batch_04/results.json</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="143" t="inlineStr">
+      <c r="A9" s="144" t="inlineStr">
         <is>
           <t>WBF-UT-015</t>
         </is>
       </c>
-      <c r="B9" s="143" t="inlineStr">
+      <c r="B9" s="144" t="inlineStr">
         <is>
           <t>y1 &gt; y2，纵向端点反向</t>
         </is>
       </c>
-      <c r="C9" s="143" t="inlineStr">
+      <c r="C9" s="144" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="D9" s="143" t="inlineStr">
+      <c r="D9" s="144" t="inlineStr">
         <is>
           <t>2026-09-11T09:34:27.731564+08:00</t>
         </is>
       </c>
-      <c r="E9" s="143" t="inlineStr">
+      <c r="E9" s="144" t="inlineStr">
         <is>
           <t>92ac4de7b79a33a81353ed8fbdadc394a45d106b</t>
         </is>
       </c>
-      <c r="F9" s="143" t="inlineStr">
+      <c r="F9" s="144" t="inlineStr">
         <is>
           <t>manual_tests/member_a/results/batch_04/results.json</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="143" t="inlineStr">
+      <c r="A10" s="144" t="inlineStr">
         <is>
           <t>WBF-UT-017</t>
         </is>
       </c>
-      <c r="B10" s="143" t="inlineStr">
+      <c r="B10" s="144" t="inlineStr">
         <is>
           <t>坐标大于1</t>
         </is>
       </c>
-      <c r="C10" s="143" t="inlineStr">
+      <c r="C10" s="144" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="D10" s="143" t="inlineStr">
+      <c r="D10" s="144" t="inlineStr">
         <is>
           <t>2026-09-11T09:35:01.042976+08:00</t>
         </is>
       </c>
-      <c r="E10" s="143" t="inlineStr">
+      <c r="E10" s="144" t="inlineStr">
         <is>
           <t>e7ca508190daedc5cf033a1d4c8f1c1f0a72cb64</t>
         </is>
       </c>
-      <c r="F10" s="143" t="inlineStr">
+      <c r="F10" s="144" t="inlineStr">
         <is>
           <t>manual_tests/member_a/results/batch_05/results.json</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="143" t="inlineStr">
+      <c r="A11" s="144" t="inlineStr">
         <is>
           <t>WBF-UT-019</t>
         </is>
       </c>
-      <c r="B11" s="143" t="inlineStr">
+      <c r="B11" s="144" t="inlineStr">
         <is>
           <t>boxes_list为空</t>
         </is>
       </c>
-      <c r="C11" s="143" t="inlineStr">
+      <c r="C11" s="144" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="D11" s="143" t="inlineStr">
+      <c r="D11" s="144" t="inlineStr">
         <is>
           <t>2026-09-11T09:35:01.042976+08:00</t>
         </is>
       </c>
-      <c r="E11" s="143" t="inlineStr">
+      <c r="E11" s="144" t="inlineStr">
         <is>
           <t>e7ca508190daedc5cf033a1d4c8f1c1f0a72cb64</t>
         </is>
       </c>
-      <c r="F11" s="143" t="inlineStr">
+      <c r="F11" s="144" t="inlineStr">
         <is>
           <t>manual_tests/member_a/results/batch_05/results.json</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="143" t="inlineStr">
+      <c r="A12" s="144" t="inlineStr">
         <is>
           <t>WBF-UT-021</t>
         </is>
       </c>
-      <c r="B12" s="143" t="inlineStr">
+      <c r="B12" s="144" t="inlineStr">
         <is>
           <t>weights = None</t>
         </is>
       </c>
-      <c r="C12" s="143" t="inlineStr">
+      <c r="C12" s="144" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D12" s="144" t="inlineStr">
+        <is>
+          <t>2026-09-11T09:35:40.300244+08:00</t>
+        </is>
+      </c>
+      <c r="E12" s="144" t="inlineStr">
+        <is>
+          <t>c2f65e6fa4b2976f4621d020a885cca49234ba2e</t>
+        </is>
+      </c>
+      <c r="F12" s="144" t="inlineStr">
+        <is>
+          <t>manual_tests/member_a/results/batch_06/results.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="144" t="inlineStr">
+        <is>
+          <t>WBF-UT-023</t>
+        </is>
+      </c>
+      <c r="B13" s="144" t="inlineStr">
+        <is>
+          <t>某模型boxes数量与scores数量不一致</t>
+        </is>
+      </c>
+      <c r="C13" s="144" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="D13" s="144" t="inlineStr">
+        <is>
+          <t>2026-09-11T09:35:40.300244+08:00</t>
+        </is>
+      </c>
+      <c r="E13" s="144" t="inlineStr">
+        <is>
+          <t>c2f65e6fa4b2976f4621d020a885cca49234ba2e</t>
+        </is>
+      </c>
+      <c r="F13" s="144" t="inlineStr">
+        <is>
+          <t>manual_tests/member_a/results/batch_06/results.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="144" t="inlineStr">
+        <is>
+          <t>WBF-UT-025</t>
+        </is>
+      </c>
+      <c r="B14" s="144" t="inlineStr">
+        <is>
+          <t>单个框只有3个坐标</t>
+        </is>
+      </c>
+      <c r="C14" s="144" t="inlineStr">
         <is>
           <t>待执行</t>
         </is>
       </c>
-      <c r="D12" s="143" t="n"/>
-      <c r="E12" s="143" t="n"/>
-      <c r="F12" s="143" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="143" t="inlineStr">
-        <is>
-          <t>WBF-UT-023</t>
-        </is>
-      </c>
-      <c r="B13" s="143" t="inlineStr">
-        <is>
-          <t>某模型boxes数量与scores数量不一致</t>
-        </is>
-      </c>
-      <c r="C13" s="143" t="inlineStr">
+      <c r="D14" s="144" t="n"/>
+      <c r="E14" s="144" t="n"/>
+      <c r="F14" s="144" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="144" t="inlineStr">
+        <is>
+          <t>WBF-UT-026</t>
+        </is>
+      </c>
+      <c r="B15" s="144" t="inlineStr">
+        <is>
+          <t>两个完全重合的同类框，score均为0</t>
+        </is>
+      </c>
+      <c r="C15" s="144" t="inlineStr">
         <is>
           <t>待执行</t>
         </is>
       </c>
-      <c r="D13" s="143" t="n"/>
-      <c r="E13" s="143" t="n"/>
-      <c r="F13" s="143" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="143" t="inlineStr">
-        <is>
-          <t>WBF-UT-025</t>
-        </is>
-      </c>
-      <c r="B14" s="143" t="inlineStr">
-        <is>
-          <t>单个框只有3个坐标</t>
-        </is>
-      </c>
-      <c r="C14" s="143" t="inlineStr">
+      <c r="D15" s="144" t="n"/>
+      <c r="E15" s="144" t="n"/>
+      <c r="F15" s="144" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="144" t="inlineStr">
+        <is>
+          <t>WBF-UT-029</t>
+        </is>
+      </c>
+      <c r="B16" s="144" t="inlineStr">
+        <is>
+          <t>合法conf_type='max'的融合坐标与最终分数</t>
+        </is>
+      </c>
+      <c r="C16" s="144" t="inlineStr">
         <is>
           <t>待执行</t>
         </is>
       </c>
-      <c r="D14" s="143" t="n"/>
-      <c r="E14" s="143" t="n"/>
-      <c r="F14" s="143" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="143" t="inlineStr">
-        <is>
-          <t>WBF-UT-026</t>
-        </is>
-      </c>
-      <c r="B15" s="143" t="inlineStr">
-        <is>
-          <t>两个完全重合的同类框，score均为0</t>
-        </is>
-      </c>
-      <c r="C15" s="143" t="inlineStr">
-        <is>
-          <t>待执行</t>
-        </is>
-      </c>
-      <c r="D15" s="143" t="n"/>
-      <c r="E15" s="143" t="n"/>
-      <c r="F15" s="143" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="143" t="inlineStr">
-        <is>
-          <t>WBF-UT-029</t>
-        </is>
-      </c>
-      <c r="B16" s="143" t="inlineStr">
-        <is>
-          <t>合法conf_type='max'的融合坐标与最终分数</t>
-        </is>
-      </c>
-      <c r="C16" s="143" t="inlineStr">
-        <is>
-          <t>待执行</t>
-        </is>
-      </c>
-      <c r="D16" s="143" t="n"/>
-      <c r="E16" s="143" t="n"/>
-      <c r="F16" s="143" t="n"/>
+      <c r="D16" s="144" t="n"/>
+      <c r="E16" s="144" t="n"/>
+      <c r="F16" s="144" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:F16"/>

--- a/docs/member_a/成员一_WBF模块1测试用例与结果.xlsx
+++ b/docs/member_a/成员一_WBF模块1测试用例与结果.xlsx
@@ -1578,7 +1578,7 @@
       <c r="I9" s="9" t="n"/>
       <c r="J9" s="11" t="inlineStr">
         <is>
-          <t>2026-09-11T09:35:40.300244+08:00</t>
+          <t>2026-09-11T09:36:50.279261+08:00</t>
         </is>
       </c>
       <c r="K9" s="11" t="n"/>
@@ -3925,7 +3925,7 @@
       <c r="M25" s="120" t="n"/>
       <c r="N25" s="43" t="n"/>
     </row>
-    <row r="26" ht="42" customHeight="1">
+    <row r="26" ht="120" customHeight="1">
       <c r="A26" s="124" t="inlineStr">
         <is>
           <t>WBF-UT-025</t>
@@ -3966,14 +3966,36 @@
           <t>boxes=[[[0.1,0.1,0.5]]]; scores=[[0.9]]; labels=[[1]]; weights=[1]</t>
         </is>
       </c>
-      <c r="I26" s="120" t="n"/>
-      <c r="J26" s="120" t="n"/>
-      <c r="K26" s="120" t="n"/>
-      <c r="L26" s="120" t="n"/>
-      <c r="M26" s="120" t="n"/>
+      <c r="I26" s="140" t="inlineStr">
+        <is>
+          <t>1. 载入test_data/member_a/WBF-UT-025.json输入。2. 使用成功复现虚拟环境运行对应pytest用例。3. 捕获返回值、形状、警告及异常，与执行前的独立预期核对。4. 保存批次日志/JSON并回填结果。</t>
+        </is>
+      </c>
+      <c r="J26" s="140" t="inlineStr">
+        <is>
+          <t>建议契约：入口拒绝非4坐标框，显式抛出ValueError并说明坐标维度；不泄漏底层IndexError。</t>
+        </is>
+      </c>
+      <c r="K26" s="140" t="inlineStr">
+        <is>
+          <t>{"scenario":"spreadsheet_input","output":null,"shapes":null,"exception":{"type":"IndexError","message":"list index out of range","exit_code":null,"traceback":"Traceback (most recent call last):\n  File \"E:\\WBF\\WBF-Software-Testing-main\\manual_tests\\member_a\\conftest.py\", line 51, in invoke\n    result = weighted_boxes_fusion(**params)\n  File \"E:\\WBF\\WBF-Software-Testing-main\\ensemble_boxes\\ensemble_boxes_wbf.py\", line 195, in weighted_boxes_fusion\n    filtered_boxes = prefilter_boxes(boxes_list, scores_list, labels_list, weights, skip_box_thr)\n  File \"E:\\WBF\\WBF-Software-Testing-main\\ensemble_boxes\\ensemble_boxes_wbf.py\", line 32, in prefilter_boxes\n    y2 = float(box_part[3])\nIndexError: list index out of range\n"},"warnings":[],"stdout":""}</t>
+        </is>
+      </c>
+      <c r="L26" s="142" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="M26" s="140" t="inlineStr">
+        <is>
+          <t>健壮性：单框维度不足；ValueError属于本次建议的健壮性要求，不宣称是原项目已有保证；错误类型差异记NG并记录为候选接口改进。
+执行时间：2026-09-11T09:36:50.279261+08:00；Python 3.10.16 / NumPy 1.23.5 / pytest 9.0.3
+运行前源码提交：55c8a207ffcbc248c3562796587427e1b744e2c5；WBF 与 reproduction-success 一致：True；证据：manual_tests/member_a/results/batch_07/results.json</t>
+        </is>
+      </c>
       <c r="N26" s="43" t="n"/>
     </row>
-    <row r="27" ht="42" customHeight="1">
+    <row r="27" ht="120" customHeight="1">
       <c r="A27" s="124" t="inlineStr">
         <is>
           <t>WBF-UT-026</t>
@@ -4014,11 +4036,33 @@
           <t>boxes=[[[0.1,0.1,0.5,0.5]],[[0.1,0.1,0.5,0.5]]]; scores=[[0],[0]]; labels=[[1],[1]]; weights=[1,1]; skip_box_thr=0; iou_thr=0.55; conf_type='avg'</t>
         </is>
       </c>
-      <c r="I27" s="120" t="n"/>
-      <c r="J27" s="120" t="n"/>
-      <c r="K27" s="120" t="n"/>
-      <c r="L27" s="120" t="n"/>
-      <c r="M27" s="120" t="n"/>
+      <c r="I27" s="140" t="inlineStr">
+        <is>
+          <t>1. 载入test_data/member_a/WBF-UT-026.json输入。2. 使用成功复现虚拟环境运行对应pytest用例。3. 捕获返回值、形状、警告及异常，与执行前的独立预期核对。4. 保存批次日志/JSON并回填结果。</t>
+        </is>
+      </c>
+      <c r="J27" s="140" t="inlineStr">
+        <is>
+          <t>不得返回NaN/Inf。可以显式ValueError拒绝，或返回形状正确且坐标/分数有限、坐标合法的结果（包含过滤后的空结果）。</t>
+        </is>
+      </c>
+      <c r="K27" s="140" t="inlineStr">
+        <is>
+          <t>{"scenario":"spreadsheet_input","output":{"boxes":[["nan","nan","nan","nan"]],"scores":[0.0],"labels":[1.0]},"shapes":[[1,4],[1],[1]],"exception":null,"warnings":[{"category":"RuntimeWarning","message":"invalid value encountered in divide"}],"stdout":""}</t>
+        </is>
+      </c>
+      <c r="L27" s="142" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="M27" s="140" t="inlineStr">
+        <is>
+          <t>数值健壮性：两个零分重合框；输入分数0等于过滤阈值0。当前契约未规定唯一零分处置，因此检查最低数值有效性，不预设必须保留或必须丢弃。
+执行时间：2026-09-11T09:36:50.279261+08:00；Python 3.10.16 / NumPy 1.23.5 / pytest 9.0.3
+运行前源码提交：55c8a207ffcbc248c3562796587427e1b744e2c5；WBF 与 reproduction-success 一致：True；证据：manual_tests/member_a/results/batch_07/results.json</t>
+        </is>
+      </c>
       <c r="N27" s="43" t="n"/>
     </row>
     <row r="28" ht="42" customHeight="1">
@@ -42335,12 +42379,24 @@
       </c>
       <c r="C14" s="144" t="inlineStr">
         <is>
-          <t>待执行</t>
-        </is>
-      </c>
-      <c r="D14" s="144" t="n"/>
-      <c r="E14" s="144" t="n"/>
-      <c r="F14" s="144" t="n"/>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="D14" s="144" t="inlineStr">
+        <is>
+          <t>2026-09-11T09:36:50.279261+08:00</t>
+        </is>
+      </c>
+      <c r="E14" s="144" t="inlineStr">
+        <is>
+          <t>55c8a207ffcbc248c3562796587427e1b744e2c5</t>
+        </is>
+      </c>
+      <c r="F14" s="144" t="inlineStr">
+        <is>
+          <t>manual_tests/member_a/results/batch_07/results.json</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="144" t="inlineStr">
@@ -42355,12 +42411,24 @@
       </c>
       <c r="C15" s="144" t="inlineStr">
         <is>
-          <t>待执行</t>
-        </is>
-      </c>
-      <c r="D15" s="144" t="n"/>
-      <c r="E15" s="144" t="n"/>
-      <c r="F15" s="144" t="n"/>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="D15" s="144" t="inlineStr">
+        <is>
+          <t>2026-09-11T09:36:50.279261+08:00</t>
+        </is>
+      </c>
+      <c r="E15" s="144" t="inlineStr">
+        <is>
+          <t>55c8a207ffcbc248c3562796587427e1b744e2c5</t>
+        </is>
+      </c>
+      <c r="F15" s="144" t="inlineStr">
+        <is>
+          <t>manual_tests/member_a/results/batch_07/results.json</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="144" t="inlineStr">

--- a/docs/member_a/成员一_WBF模块1测试用例与结果.xlsx
+++ b/docs/member_a/成员一_WBF模块1测试用例与结果.xlsx
@@ -1578,7 +1578,7 @@
       <c r="I9" s="9" t="n"/>
       <c r="J9" s="11" t="inlineStr">
         <is>
-          <t>2026-09-11T09:36:50.279261+08:00</t>
+          <t>2026-09-11T09:38:31.029285+08:00</t>
         </is>
       </c>
       <c r="K9" s="11" t="n"/>
@@ -4161,7 +4161,7 @@
       <c r="M29" s="120" t="n"/>
       <c r="N29" s="43" t="n"/>
     </row>
-    <row r="30" ht="42" customHeight="1">
+    <row r="30" ht="120" customHeight="1">
       <c r="A30" s="124" t="inlineStr">
         <is>
           <t>WBF-UT-029</t>
@@ -4202,11 +4202,33 @@
           <t>boxes=[[[0.1,0.1,0.5,0.5]],[[0.15,0.1,0.55,0.5]]]; scores=[[0.9],[0.8]]; labels=[[1],[1]]; weights=[2,1]; iou_thr=0.55; conf_type='max'</t>
         </is>
       </c>
-      <c r="I30" s="120" t="n"/>
-      <c r="J30" s="120" t="n"/>
-      <c r="K30" s="120" t="n"/>
-      <c r="L30" s="120" t="n"/>
-      <c r="M30" s="120" t="n"/>
+      <c r="I30" s="140" t="inlineStr">
+        <is>
+          <t>1. 载入test_data/member_a/WBF-UT-029.json输入。2. 使用成功复现虚拟环境运行对应pytest用例。3. 捕获返回值、形状、警告及异常，与执行前的独立预期核对。4. 保存批次日志/JSON并回填结果。</t>
+        </is>
+      </c>
+      <c r="J30" s="140" t="inlineStr">
+        <is>
+          <t>融合1框，坐标约[0.1153846154,0.1,0.5153846154,0.5]；分数0.9、类别1。</t>
+        </is>
+      </c>
+      <c r="K30" s="140" t="inlineStr">
+        <is>
+          <t>{"scenario":"spreadsheet_input","output":{"boxes":[[0.11538462340831757,0.10000000894069672,0.5153846740722656,0.5]],"scores":[0.8999999761581421],"labels":[1.0]},"shapes":[[1,4],[1],[1]],"exception":null,"warnings":[],"stdout":""}</t>
+        </is>
+      </c>
+      <c r="L30" s="141" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="M30" s="140" t="inlineStr">
+        <is>
+          <t>手工计算：max模式的坐标和分数；有效权重0.9×2=1.8和0.8×1=0.8；坐标按1.8/0.8加权（非直接取最高分框）；max分数=max(1.8,0.8)/max(2,1)=0.9。
+执行时间：2026-09-11T09:38:31.029285+08:00；Python 3.10.16 / NumPy 1.23.5 / pytest 9.0.3
+运行前源码提交：105b2ffe920b154c50c45a8a328dc0273c9ef0d2；WBF 与 reproduction-success 一致：True；证据：manual_tests/member_a/results/batch_08/results.json</t>
+        </is>
+      </c>
       <c r="N30" s="43" t="n"/>
     </row>
     <row r="31" ht="42" customHeight="1">
@@ -42443,12 +42465,24 @@
       </c>
       <c r="C16" s="144" t="inlineStr">
         <is>
-          <t>待执行</t>
-        </is>
-      </c>
-      <c r="D16" s="144" t="n"/>
-      <c r="E16" s="144" t="n"/>
-      <c r="F16" s="144" t="n"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D16" s="144" t="inlineStr">
+        <is>
+          <t>2026-09-11T09:38:31.029285+08:00</t>
+        </is>
+      </c>
+      <c r="E16" s="144" t="inlineStr">
+        <is>
+          <t>105b2ffe920b154c50c45a8a328dc0273c9ef0d2</t>
+        </is>
+      </c>
+      <c r="F16" s="144" t="inlineStr">
+        <is>
+          <t>manual_tests/member_a/results/batch_08/results.json</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:F16"/>
